--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D8104CA-55EB-46A3-B303-5C27F759170F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D01D7328-0CF2-47B8-8A7C-69A2E4B95D61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D714F249-A04F-4212-A361-05AD51F3A279}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B6375A1-AA51-4AE4-BCD7-907C10D7DC12}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C22CDC87-7916-4758-941C-8841C2F234B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D25FD9D8-DAEB-4357-BBE4-E00625948D40}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D01D7328-0CF2-47B8-8A7C-69A2E4B95D61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A242DD28-7AD0-4DDB-99CD-92BF65265EC6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B6375A1-AA51-4AE4-BCD7-907C10D7DC12}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C20F1287-BB16-41BE-9FB2-81C1484B0223}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D25FD9D8-DAEB-4357-BBE4-E00625948D40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F655E021-185C-43B6-8349-B96194F3495B}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A242DD28-7AD0-4DDB-99CD-92BF65265EC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BD33788-1332-4F29-AC76-B44DF8CAA080}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C20F1287-BB16-41BE-9FB2-81C1484B0223}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDDB85E-A99C-45F1-A2CD-D8F74868A707}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F655E021-185C-43B6-8349-B96194F3495B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0439B469-BD3F-42C4-AB5A-9D66F2E354B5}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BD33788-1332-4F29-AC76-B44DF8CAA080}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03F47755-30C1-42AB-BFFB-65F6B3CD67A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDDB85E-A99C-45F1-A2CD-D8F74868A707}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01905397-352B-40B3-9D46-25E30D136158}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0439B469-BD3F-42C4-AB5A-9D66F2E354B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{077318ED-86D4-49C8-8404-B68B3AA50F5F}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03F47755-30C1-42AB-BFFB-65F6B3CD67A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9195415B-AB26-45A1-8AF5-E41969D81082}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01905397-352B-40B3-9D46-25E30D136158}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CBE7D69-372D-41C4-8346-CD7332FF5B3A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{077318ED-86D4-49C8-8404-B68B3AA50F5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CC5948-764D-4B99-AC7D-A342340AEE28}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1090,22 +1090,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BD33788-1332-4F29-AC76-B44DF8CAA080}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD1D842B-F269-4814-A5D5-79397AF1AD16}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDDB85E-A99C-45F1-A2CD-D8F74868A707}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA0E3F20-3F8F-40F4-97BD-6B552492F111}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0439B469-BD3F-42C4-AB5A-9D66F2E354B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F29C278-5362-4C13-B8B0-89E8DD58C173}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1090,22 +1090,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9195415B-AB26-45A1-8AF5-E41969D81082}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{444B988A-0BC2-4F24-96A6-43FE54C7FE45}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CBE7D69-372D-41C4-8346-CD7332FF5B3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C4743E5-610E-4082-A251-34D39CA06BF6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18CC5948-764D-4B99-AC7D-A342340AEE28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE41855-DACA-466D-B6A5-A5251F4728C4}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{444B988A-0BC2-4F24-96A6-43FE54C7FE45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60DB4018-DB8F-4EA4-AF71-531D4C501915}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C4743E5-610E-4082-A251-34D39CA06BF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCD84288-C851-483A-A543-0E2A3D79A742}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE41855-DACA-466D-B6A5-A5251F4728C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{616AAA80-4B48-4610-BE34-D92185FAE832}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60DB4018-DB8F-4EA4-AF71-531D4C501915}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10DA84C8-F174-4B02-8082-C4988F4A8A17}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCD84288-C851-483A-A543-0E2A3D79A742}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51D44ED1-109E-4CD6-A320-AAABBDAC28CE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{616AAA80-4B48-4610-BE34-D92185FAE832}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E0891C-4F0D-47CC-A3E1-0F0DC4B2DE51}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10DA84C8-F174-4B02-8082-C4988F4A8A17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9373A1-E393-466E-AF57-8DB8E1782EA4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51D44ED1-109E-4CD6-A320-AAABBDAC28CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCBC1658-68D4-4469-B66D-1970C62E2AE2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E0891C-4F0D-47CC-A3E1-0F0DC4B2DE51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85502604-446C-4903-8D67-9FCB22801B45}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C9373A1-E393-466E-AF57-8DB8E1782EA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83B15BC-64BC-4723-84C8-63CE6F788266}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCBC1658-68D4-4469-B66D-1970C62E2AE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8C3825-383C-47EA-BDA2-3D11733004E9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85502604-446C-4903-8D67-9FCB22801B45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB97C1A2-7367-4F71-ADC1-22F7D34DD40C}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83B15BC-64BC-4723-84C8-63CE6F788266}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30FC2C48-535B-493A-9E2B-298D4ECAD198}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8C3825-383C-47EA-BDA2-3D11733004E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4A276B2-1547-4448-9BD8-1C1719C79706}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB97C1A2-7367-4F71-ADC1-22F7D34DD40C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C018B79-F4B5-45E1-BF4D-FA4DF31AB04F}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30FC2C48-535B-493A-9E2B-298D4ECAD198}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE853415-11F2-42FE-9B41-869AD155D1C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4A276B2-1547-4448-9BD8-1C1719C79706}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11DEB366-09D4-48E8-B6DC-9EC116BD2C63}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C018B79-F4B5-45E1-BF4D-FA4DF31AB04F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D44BAA-2323-4671-8A2A-299A36BA19E2}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE853415-11F2-42FE-9B41-869AD155D1C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE2F4A89-BC93-4584-9C9E-3BA1D3E3F2A4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11DEB366-09D4-48E8-B6DC-9EC116BD2C63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11506AF8-EE17-413C-986B-0A918A10D9B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7D44BAA-2323-4671-8A2A-299A36BA19E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8ED23A5-C40D-41A3-A1D3-FAC1E641E826}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE2F4A89-BC93-4584-9C9E-3BA1D3E3F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35578BEE-4095-4961-9596-FCABDA09F90B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11506AF8-EE17-413C-986B-0A918A10D9B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBA3564-C175-48D0-82B0-81FDD2961883}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8ED23A5-C40D-41A3-A1D3-FAC1E641E826}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B886A2A-3016-4C3E-985C-6EBAE498701D}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35578BEE-4095-4961-9596-FCABDA09F90B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB1580E-B06F-49BD-B2AA-E7043C11A6DF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EBA3564-C175-48D0-82B0-81FDD2961883}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7372392E-6896-47A0-9BD4-D387C1FCBF65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B886A2A-3016-4C3E-985C-6EBAE498701D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{128F879B-368C-4117-9C84-3728CD4B4A42}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AB1580E-B06F-49BD-B2AA-E7043C11A6DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4F13993-E91F-4EBF-9793-8E5D0F408BB6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7372392E-6896-47A0-9BD4-D387C1FCBF65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AE4502-750F-47D6-9241-C20D0AD86813}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{128F879B-368C-4117-9C84-3728CD4B4A42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AEA9EDF-8A1A-4338-877D-45C9EA1C94C0}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4F13993-E91F-4EBF-9793-8E5D0F408BB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA9394A0-1289-4482-BAE7-2B074B070A1F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2AE4502-750F-47D6-9241-C20D0AD86813}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30651209-731C-449B-A839-6B8963D79486}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AEA9EDF-8A1A-4338-877D-45C9EA1C94C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD788151-1FC2-4F72-B75D-9E637A6D5245}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA9394A0-1289-4482-BAE7-2B074B070A1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A14E7B76-68C0-4335-BE58-270C45977414}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30651209-731C-449B-A839-6B8963D79486}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93B218B3-C47D-4BBA-BCC9-B3BAFE6CB299}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD788151-1FC2-4F72-B75D-9E637A6D5245}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CED99379-A3E8-4012-AE2D-1A67D3620042}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A14E7B76-68C0-4335-BE58-270C45977414}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DFC28B9-67B0-474F-9608-7B717EB91424}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93B218B3-C47D-4BBA-BCC9-B3BAFE6CB299}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C9E654F-47AA-4954-9844-01367F22F702}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CED99379-A3E8-4012-AE2D-1A67D3620042}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7151D3B3-AE52-4436-BB19-15F5BECB5A86}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DFC28B9-67B0-474F-9608-7B717EB91424}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A74ADD-3866-45B0-BF5F-31B090674A79}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C9E654F-47AA-4954-9844-01367F22F702}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE2A1A75-B626-493A-8AFD-023EE744B388}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7151D3B3-AE52-4436-BB19-15F5BECB5A86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E41F2A3-B04C-4B3B-8062-52623C447FB5}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A74ADD-3866-45B0-BF5F-31B090674A79}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B21447E3-F03C-43E6-B402-D94D7EC47DD3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE2A1A75-B626-493A-8AFD-023EE744B388}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5871FD-D493-4211-B99C-48AAE0EA665F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E41F2A3-B04C-4B3B-8062-52623C447FB5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57CDED74-974C-44E8-8044-3DDD7D229CF9}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B21447E3-F03C-43E6-B402-D94D7EC47DD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47E6292A-99C0-4943-B4CA-8D6D3A420A34}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5871FD-D493-4211-B99C-48AAE0EA665F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FA47B75-E0C3-4433-BA05-0B5458441FC2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57CDED74-974C-44E8-8044-3DDD7D229CF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAD1910-D079-43EE-AA2E-289EB525F5FD}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47E6292A-99C0-4943-B4CA-8D6D3A420A34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{487A95C2-BFBB-4C9E-BC37-40B391A81F0B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FA47B75-E0C3-4433-BA05-0B5458441FC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BD8AFFC-64A1-4BED-A321-AF2EE43ECD45}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAD1910-D079-43EE-AA2E-289EB525F5FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAC04B30-F680-4061-882B-55555A59591F}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{487A95C2-BFBB-4C9E-BC37-40B391A81F0B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA38D2CD-9B95-489B-95D4-2104110F7A35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BD8AFFC-64A1-4BED-A321-AF2EE43ECD45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D84DCA-1109-499E-A832-46A8B576490F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAC04B30-F680-4061-882B-55555A59591F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB36C7E-0E30-4D1E-927D-7FD0D3DDB520}"/>
 </file>
--- a/____EvoM1_TraitTable/v1_synapses_karl.xlsx
+++ b/____EvoM1_TraitTable/v1_synapses_karl.xlsx
@@ -1099,13 +1099,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA38D2CD-9B95-489B-95D4-2104110F7A35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{886778BD-E560-476F-ACFE-4F66AC2D97FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D84DCA-1109-499E-A832-46A8B576490F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E7988F2-1253-496C-91EB-90D21A56710E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CB36C7E-0E30-4D1E-927D-7FD0D3DDB520}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{760E50AD-16C8-4277-8809-5F0109D044E6}"/>
 </file>